--- a/지급률_v0.xlsx
+++ b/지급률_v0.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\InKyoung\ALM\기초지수\20251118\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{618EC65D-51CC-4269-96E4-A3D7C8D16BC0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AE98B36-588F-4DCF-8F79-F1B2332033A2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,10 +60,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -118,6 +120,14 @@
       <color indexed="8"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -222,14 +232,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -257,8 +270,18 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
+    <cellStyle name="쉼표 [0]" xfId="3" builtinId="6"/>
     <cellStyle name="쉼표 [0] 5" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="표준 18" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
@@ -540,15 +563,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:L72"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.75" customWidth="1"/>
     <col min="2" max="3" width="11.125" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -571,7 +596,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -582,7 +607,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="2">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2">
         <v>0</v>
@@ -593,8 +618,9 @@
       <c r="G2" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="L2" s="9"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -606,11 +632,11 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E3" s="4">
         <f>+E2+D3</f>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F3" s="4">
         <v>2</v>
@@ -619,8 +645,9 @@
         <f>+G2+F3</f>
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="L3" s="9"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -632,11 +659,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="4">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E4" s="4">
         <f t="shared" ref="E4" si="1">+E3+D4</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" s="4">
         <v>2</v>
@@ -645,8 +672,9 @@
         <f t="shared" ref="G4" si="2">+G3+F4</f>
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="L4" s="9"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -658,11 +686,11 @@
         <v>3</v>
       </c>
       <c r="D5" s="4">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E5" s="4">
         <f>+E4+D5</f>
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="F5" s="4">
         <v>2</v>
@@ -671,8 +699,9 @@
         <f>+G4+F5</f>
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="L5" s="9"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -684,11 +713,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="6">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="E6" s="6">
         <f t="shared" ref="E6:E19" si="4">+E5+D6</f>
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="F6" s="6">
         <v>2</v>
@@ -697,8 +726,11 @@
         <f t="shared" ref="G6:G19" si="5">+G5+F6</f>
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I6" s="10"/>
+      <c r="J6" s="11"/>
+      <c r="L6" s="9"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -710,11 +742,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="2">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="E7" s="2">
         <f t="shared" si="4"/>
-        <v>7.5</v>
+        <v>5.6</v>
       </c>
       <c r="F7" s="2">
         <v>2</v>
@@ -723,8 +755,9 @@
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="L7" s="9"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -740,7 +773,7 @@
       </c>
       <c r="E8" s="4">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>7.1</v>
       </c>
       <c r="F8" s="4">
         <v>2</v>
@@ -750,7 +783,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -766,7 +799,7 @@
       </c>
       <c r="E9" s="4">
         <f t="shared" si="4"/>
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="F9" s="4">
         <v>2</v>
@@ -776,7 +809,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -788,11 +821,11 @@
         <v>8</v>
       </c>
       <c r="D10" s="4">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="E10" s="4">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>10.299999999999999</v>
       </c>
       <c r="F10" s="4">
         <v>2</v>
@@ -802,7 +835,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>9</v>
       </c>
@@ -814,11 +847,11 @@
         <v>9</v>
       </c>
       <c r="D11" s="6">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="E11" s="6">
         <f t="shared" si="4"/>
-        <v>13.5</v>
+        <v>11.999999999999998</v>
       </c>
       <c r="F11" s="6">
         <v>2</v>
@@ -828,7 +861,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -840,11 +873,11 @@
         <v>10</v>
       </c>
       <c r="D12" s="2">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="E12" s="2">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>13.699999999999998</v>
       </c>
       <c r="F12" s="2">
         <v>2</v>
@@ -854,7 +887,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -866,11 +899,11 @@
         <v>11</v>
       </c>
       <c r="D13" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E13" s="4">
         <f t="shared" si="4"/>
-        <v>16.5</v>
+        <v>15.699999999999998</v>
       </c>
       <c r="F13" s="4">
         <v>2</v>
@@ -880,7 +913,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -892,11 +925,11 @@
         <v>12</v>
       </c>
       <c r="D14" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E14" s="4">
         <f t="shared" si="4"/>
-        <v>18</v>
+        <v>17.699999999999996</v>
       </c>
       <c r="F14" s="4">
         <v>2</v>
@@ -906,7 +939,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -918,11 +951,11 @@
         <v>13</v>
       </c>
       <c r="D15" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E15" s="4">
         <f t="shared" si="4"/>
-        <v>19.5</v>
+        <v>19.699999999999996</v>
       </c>
       <c r="F15" s="4">
         <v>2</v>
@@ -932,7 +965,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>14</v>
       </c>
@@ -943,12 +976,12 @@
         <f t="shared" si="3"/>
         <v>14</v>
       </c>
-      <c r="D16" s="6">
-        <v>1.5</v>
+      <c r="D16" s="4">
+        <v>2</v>
       </c>
       <c r="E16" s="6">
         <f t="shared" si="4"/>
-        <v>21</v>
+        <v>21.699999999999996</v>
       </c>
       <c r="F16" s="6">
         <v>2</v>
@@ -970,11 +1003,11 @@
         <v>15</v>
       </c>
       <c r="D17" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E17" s="2">
         <f t="shared" si="4"/>
-        <v>22.5</v>
+        <v>23.699999999999996</v>
       </c>
       <c r="F17" s="2">
         <v>2</v>
@@ -996,11 +1029,11 @@
         <v>16</v>
       </c>
       <c r="D18" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E18" s="4">
         <f t="shared" si="4"/>
-        <v>24</v>
+        <v>25.699999999999996</v>
       </c>
       <c r="F18" s="4">
         <v>2</v>
@@ -1022,11 +1055,11 @@
         <v>17</v>
       </c>
       <c r="D19" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E19" s="4">
         <f t="shared" si="4"/>
-        <v>25.5</v>
+        <v>27.699999999999996</v>
       </c>
       <c r="F19" s="4">
         <v>2</v>
@@ -1048,11 +1081,11 @@
         <v>18</v>
       </c>
       <c r="D20" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E20" s="4">
         <f>+E19+D20</f>
-        <v>27</v>
+        <v>29.699999999999996</v>
       </c>
       <c r="F20" s="4">
         <v>2</v>
@@ -1073,12 +1106,12 @@
         <f>+C20+B21</f>
         <v>19</v>
       </c>
-      <c r="D21" s="6">
-        <v>1.5</v>
+      <c r="D21" s="4">
+        <v>2</v>
       </c>
       <c r="E21" s="6">
         <f>+E20+D21</f>
-        <v>28.5</v>
+        <v>31.699999999999996</v>
       </c>
       <c r="F21" s="6">
         <v>2</v>
@@ -1100,11 +1133,11 @@
         <v>20</v>
       </c>
       <c r="D22" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E22" s="2">
         <f>+E21+D22</f>
-        <v>30</v>
+        <v>33.699999999999996</v>
       </c>
       <c r="F22" s="2">
         <v>2</v>
@@ -1126,11 +1159,11 @@
         <v>21</v>
       </c>
       <c r="D23" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E23" s="4">
         <f t="shared" ref="E23:E72" si="7">+E22+D23</f>
-        <v>31.5</v>
+        <v>35.699999999999996</v>
       </c>
       <c r="F23" s="4">
         <v>2</v>
@@ -1152,11 +1185,11 @@
         <v>22</v>
       </c>
       <c r="D24" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E24" s="4">
         <f t="shared" si="7"/>
-        <v>33</v>
+        <v>37.699999999999996</v>
       </c>
       <c r="F24" s="4">
         <v>2</v>
@@ -1178,11 +1211,11 @@
         <v>23</v>
       </c>
       <c r="D25" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E25" s="4">
         <f t="shared" si="7"/>
-        <v>34.5</v>
+        <v>39.699999999999996</v>
       </c>
       <c r="F25" s="4">
         <v>2</v>
@@ -1203,12 +1236,12 @@
         <f t="shared" si="6"/>
         <v>24</v>
       </c>
-      <c r="D26" s="6">
-        <v>1.5</v>
+      <c r="D26" s="4">
+        <v>2</v>
       </c>
       <c r="E26" s="6">
         <f t="shared" si="7"/>
-        <v>36</v>
+        <v>41.699999999999996</v>
       </c>
       <c r="F26" s="6">
         <v>2</v>
@@ -1230,11 +1263,11 @@
         <v>25</v>
       </c>
       <c r="D27" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E27" s="2">
         <f t="shared" si="7"/>
-        <v>37.5</v>
+        <v>43.699999999999996</v>
       </c>
       <c r="F27" s="2">
         <v>2</v>
@@ -1256,11 +1289,11 @@
         <v>26</v>
       </c>
       <c r="D28" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E28" s="4">
         <f t="shared" si="7"/>
-        <v>39</v>
+        <v>45.699999999999996</v>
       </c>
       <c r="F28" s="4">
         <v>2</v>
@@ -1282,11 +1315,11 @@
         <v>27</v>
       </c>
       <c r="D29" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E29" s="4">
         <f t="shared" si="7"/>
-        <v>40.5</v>
+        <v>47.699999999999996</v>
       </c>
       <c r="F29" s="4">
         <v>2</v>
@@ -1308,11 +1341,11 @@
         <v>28</v>
       </c>
       <c r="D30" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E30" s="4">
         <f t="shared" si="7"/>
-        <v>42</v>
+        <v>49.699999999999996</v>
       </c>
       <c r="F30" s="4">
         <v>2</v>
@@ -1333,12 +1366,12 @@
         <f t="shared" si="6"/>
         <v>29</v>
       </c>
-      <c r="D31" s="6">
-        <v>1.5</v>
+      <c r="D31" s="4">
+        <v>2</v>
       </c>
       <c r="E31" s="6">
         <f t="shared" si="7"/>
-        <v>43.5</v>
+        <v>51.699999999999996</v>
       </c>
       <c r="F31" s="6">
         <v>2</v>
@@ -1360,11 +1393,11 @@
         <v>30</v>
       </c>
       <c r="D32" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E32" s="2">
         <f t="shared" si="7"/>
-        <v>45</v>
+        <v>53.699999999999996</v>
       </c>
       <c r="F32" s="2">
         <v>2</v>
@@ -1386,11 +1419,11 @@
         <v>31</v>
       </c>
       <c r="D33" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E33" s="4">
         <f t="shared" si="7"/>
-        <v>46.5</v>
+        <v>55.699999999999996</v>
       </c>
       <c r="F33" s="4">
         <v>2</v>
@@ -1412,11 +1445,11 @@
         <v>32</v>
       </c>
       <c r="D34" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E34" s="4">
         <f t="shared" si="7"/>
-        <v>48</v>
+        <v>57.699999999999996</v>
       </c>
       <c r="F34" s="4">
         <v>2</v>
@@ -1438,11 +1471,11 @@
         <v>33</v>
       </c>
       <c r="D35" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E35" s="4">
         <f t="shared" si="7"/>
-        <v>49.5</v>
+        <v>59.699999999999996</v>
       </c>
       <c r="F35" s="4">
         <v>2</v>
@@ -1463,12 +1496,12 @@
         <f t="shared" si="6"/>
         <v>34</v>
       </c>
-      <c r="D36" s="6">
-        <v>1.5</v>
+      <c r="D36" s="4">
+        <v>2</v>
       </c>
       <c r="E36" s="6">
         <f t="shared" si="7"/>
-        <v>51</v>
+        <v>61.699999999999996</v>
       </c>
       <c r="F36" s="6">
         <v>2</v>
@@ -1490,11 +1523,11 @@
         <v>35</v>
       </c>
       <c r="D37" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E37" s="2">
         <f t="shared" si="7"/>
-        <v>52.5</v>
+        <v>63.699999999999996</v>
       </c>
       <c r="F37" s="2">
         <v>2</v>
@@ -1516,11 +1549,11 @@
         <v>36</v>
       </c>
       <c r="D38" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E38" s="4">
         <f t="shared" si="7"/>
-        <v>54</v>
+        <v>65.699999999999989</v>
       </c>
       <c r="F38" s="4">
         <v>2</v>
@@ -1542,11 +1575,11 @@
         <v>37</v>
       </c>
       <c r="D39" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E39" s="4">
         <f t="shared" si="7"/>
-        <v>55.5</v>
+        <v>67.699999999999989</v>
       </c>
       <c r="F39" s="4">
         <v>2</v>
@@ -1568,11 +1601,11 @@
         <v>38</v>
       </c>
       <c r="D40" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E40" s="4">
         <f t="shared" si="7"/>
-        <v>57</v>
+        <v>69.699999999999989</v>
       </c>
       <c r="F40" s="4">
         <v>2</v>
@@ -1593,12 +1626,12 @@
         <f t="shared" si="6"/>
         <v>39</v>
       </c>
-      <c r="D41" s="6">
-        <v>1.5</v>
+      <c r="D41" s="4">
+        <v>2</v>
       </c>
       <c r="E41" s="6">
         <f t="shared" si="7"/>
-        <v>58.5</v>
+        <v>71.699999999999989</v>
       </c>
       <c r="F41" s="6">
         <v>2</v>
@@ -1620,11 +1653,11 @@
         <v>40</v>
       </c>
       <c r="D42" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E42" s="2">
         <f t="shared" si="7"/>
-        <v>60</v>
+        <v>73.699999999999989</v>
       </c>
       <c r="F42" s="2">
         <v>2</v>
@@ -1646,11 +1679,11 @@
         <v>41</v>
       </c>
       <c r="D43" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E43" s="4">
         <f t="shared" si="7"/>
-        <v>61.5</v>
+        <v>75.699999999999989</v>
       </c>
       <c r="F43" s="4">
         <v>2</v>
@@ -1672,11 +1705,11 @@
         <v>42</v>
       </c>
       <c r="D44" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E44" s="4">
         <f t="shared" si="7"/>
-        <v>63</v>
+        <v>77.699999999999989</v>
       </c>
       <c r="F44" s="4">
         <v>2</v>
@@ -1698,11 +1731,11 @@
         <v>43</v>
       </c>
       <c r="D45" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E45" s="4">
         <f t="shared" si="7"/>
-        <v>64.5</v>
+        <v>79.699999999999989</v>
       </c>
       <c r="F45" s="4">
         <v>2</v>
@@ -1723,12 +1756,12 @@
         <f t="shared" si="6"/>
         <v>44</v>
       </c>
-      <c r="D46" s="6">
-        <v>1.5</v>
+      <c r="D46" s="4">
+        <v>2</v>
       </c>
       <c r="E46" s="6">
         <f t="shared" si="7"/>
-        <v>66</v>
+        <v>81.699999999999989</v>
       </c>
       <c r="F46" s="6">
         <v>2</v>
@@ -1750,11 +1783,11 @@
         <v>45</v>
       </c>
       <c r="D47" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E47" s="2">
         <f t="shared" si="7"/>
-        <v>67.5</v>
+        <v>83.699999999999989</v>
       </c>
       <c r="F47" s="2">
         <v>2</v>
@@ -1776,11 +1809,11 @@
         <v>46</v>
       </c>
       <c r="D48" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E48" s="4">
         <f t="shared" si="7"/>
-        <v>69</v>
+        <v>85.699999999999989</v>
       </c>
       <c r="F48" s="4">
         <v>2</v>
@@ -1802,11 +1835,11 @@
         <v>47</v>
       </c>
       <c r="D49" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E49" s="4">
         <f t="shared" si="7"/>
-        <v>70.5</v>
+        <v>87.699999999999989</v>
       </c>
       <c r="F49" s="4">
         <v>2</v>
@@ -1828,11 +1861,11 @@
         <v>48</v>
       </c>
       <c r="D50" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E50" s="4">
         <f t="shared" si="7"/>
-        <v>72</v>
+        <v>89.699999999999989</v>
       </c>
       <c r="F50" s="4">
         <v>2</v>
@@ -1853,12 +1886,12 @@
         <f t="shared" si="6"/>
         <v>49</v>
       </c>
-      <c r="D51" s="6">
-        <v>1.5</v>
+      <c r="D51" s="4">
+        <v>2</v>
       </c>
       <c r="E51" s="6">
         <f t="shared" si="7"/>
-        <v>73.5</v>
+        <v>91.699999999999989</v>
       </c>
       <c r="F51" s="6">
         <v>2</v>
@@ -1880,11 +1913,11 @@
         <v>50</v>
       </c>
       <c r="D52" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E52" s="2">
         <f t="shared" si="7"/>
-        <v>75</v>
+        <v>93.699999999999989</v>
       </c>
       <c r="F52" s="2">
         <v>2</v>
@@ -1906,11 +1939,11 @@
         <v>51</v>
       </c>
       <c r="D53" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E53" s="4">
         <f t="shared" si="7"/>
-        <v>76.5</v>
+        <v>95.699999999999989</v>
       </c>
       <c r="F53" s="4">
         <v>2</v>
@@ -1932,11 +1965,11 @@
         <v>52</v>
       </c>
       <c r="D54" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E54" s="4">
         <f t="shared" si="7"/>
-        <v>78</v>
+        <v>97.699999999999989</v>
       </c>
       <c r="F54" s="4">
         <v>2</v>
@@ -1958,11 +1991,11 @@
         <v>53</v>
       </c>
       <c r="D55" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E55" s="4">
         <f t="shared" si="7"/>
-        <v>79.5</v>
+        <v>99.699999999999989</v>
       </c>
       <c r="F55" s="4">
         <v>2</v>
@@ -1983,12 +2016,12 @@
         <f t="shared" si="6"/>
         <v>54</v>
       </c>
-      <c r="D56" s="6">
-        <v>1.5</v>
+      <c r="D56" s="4">
+        <v>2</v>
       </c>
       <c r="E56" s="6">
         <f t="shared" si="7"/>
-        <v>81</v>
+        <v>101.69999999999999</v>
       </c>
       <c r="F56" s="6">
         <v>2</v>
@@ -2010,11 +2043,11 @@
         <v>55</v>
       </c>
       <c r="D57" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E57" s="2">
         <f t="shared" si="7"/>
-        <v>82.5</v>
+        <v>103.69999999999999</v>
       </c>
       <c r="F57" s="2">
         <v>2</v>
@@ -2037,11 +2070,11 @@
         <v>56</v>
       </c>
       <c r="D58" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E58" s="4">
         <f t="shared" si="7"/>
-        <v>84</v>
+        <v>105.69999999999999</v>
       </c>
       <c r="F58" s="4">
         <v>2</v>
@@ -2064,11 +2097,11 @@
         <v>57</v>
       </c>
       <c r="D59" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E59" s="4">
         <f t="shared" si="7"/>
-        <v>85.5</v>
+        <v>107.69999999999999</v>
       </c>
       <c r="F59" s="4">
         <v>2</v>
@@ -2091,11 +2124,11 @@
         <v>58</v>
       </c>
       <c r="D60" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E60" s="4">
         <f t="shared" si="7"/>
-        <v>87</v>
+        <v>109.69999999999999</v>
       </c>
       <c r="F60" s="4">
         <v>2</v>
@@ -2117,12 +2150,12 @@
         <f t="shared" si="6"/>
         <v>59</v>
       </c>
-      <c r="D61" s="6">
-        <v>1.5</v>
+      <c r="D61" s="4">
+        <v>2</v>
       </c>
       <c r="E61" s="6">
         <f t="shared" si="7"/>
-        <v>88.5</v>
+        <v>111.69999999999999</v>
       </c>
       <c r="F61" s="6">
         <v>2</v>
@@ -2145,11 +2178,11 @@
         <v>60</v>
       </c>
       <c r="D62" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E62" s="2">
         <f t="shared" si="7"/>
-        <v>90</v>
+        <v>113.69999999999999</v>
       </c>
       <c r="F62" s="2">
         <v>2</v>
@@ -2172,11 +2205,11 @@
         <v>61</v>
       </c>
       <c r="D63" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E63" s="4">
         <f t="shared" si="7"/>
-        <v>91.5</v>
+        <v>115.69999999999999</v>
       </c>
       <c r="F63" s="4">
         <v>2</v>
@@ -2199,11 +2232,11 @@
         <v>62</v>
       </c>
       <c r="D64" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E64" s="4">
         <f t="shared" si="7"/>
-        <v>93</v>
+        <v>117.69999999999999</v>
       </c>
       <c r="F64" s="4">
         <v>2</v>
@@ -2226,11 +2259,11 @@
         <v>63</v>
       </c>
       <c r="D65" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E65" s="4">
         <f t="shared" si="7"/>
-        <v>94.5</v>
+        <v>119.69999999999999</v>
       </c>
       <c r="F65" s="4">
         <v>2</v>
@@ -2253,11 +2286,11 @@
         <v>64</v>
       </c>
       <c r="D66" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E66" s="4">
         <f t="shared" si="7"/>
-        <v>96</v>
+        <v>121.69999999999999</v>
       </c>
       <c r="F66" s="4">
         <v>2</v>
@@ -2280,11 +2313,11 @@
         <v>65</v>
       </c>
       <c r="D67" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E67" s="2">
         <f t="shared" si="7"/>
-        <v>97.5</v>
+        <v>123.69999999999999</v>
       </c>
       <c r="F67" s="2">
         <v>2</v>
@@ -2307,11 +2340,11 @@
         <v>66</v>
       </c>
       <c r="D68" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E68" s="4">
         <f t="shared" si="7"/>
-        <v>99</v>
+        <v>125.69999999999999</v>
       </c>
       <c r="F68" s="4">
         <v>2</v>
@@ -2334,11 +2367,11 @@
         <v>67</v>
       </c>
       <c r="D69" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E69" s="4">
         <f t="shared" si="7"/>
-        <v>100.5</v>
+        <v>127.69999999999999</v>
       </c>
       <c r="F69" s="4">
         <v>2</v>
@@ -2361,11 +2394,11 @@
         <v>68</v>
       </c>
       <c r="D70" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E70" s="4">
         <f t="shared" si="7"/>
-        <v>102</v>
+        <v>129.69999999999999</v>
       </c>
       <c r="F70" s="4">
         <v>2</v>
@@ -2388,11 +2421,11 @@
         <v>69</v>
       </c>
       <c r="D71" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E71" s="4">
         <f t="shared" si="7"/>
-        <v>103.5</v>
+        <v>131.69999999999999</v>
       </c>
       <c r="F71" s="4">
         <v>2</v>
@@ -2415,11 +2448,11 @@
         <v>70</v>
       </c>
       <c r="D72" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E72" s="2">
         <f t="shared" si="7"/>
-        <v>105</v>
+        <v>133.69999999999999</v>
       </c>
       <c r="F72" s="2">
         <v>2</v>
